--- a/week_3/SyntheticData.xlsx
+++ b/week_3/SyntheticData.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uyanwune chekwube\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uyanwune chekwube\Downloads\CreditRiskAnalysis\week_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="2" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="17" r:id="rId1"/>
@@ -27,9 +27,8 @@
   </externalReferences>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="4" r:id="rId11"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="290">
   <si>
     <t>signup_date</t>
   </si>
@@ -459,12 +458,6 @@
   </si>
   <si>
     <t>Clement Orji</t>
-  </si>
-  <si>
-    <t>LO16</t>
-  </si>
-  <si>
-    <t>LO11</t>
   </si>
   <si>
     <t>Null</t>
@@ -928,7 +921,7 @@
     <numFmt numFmtId="166" formatCode="\₦#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -971,18 +964,18 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -995,62 +988,68 @@
       <sz val="1"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1138,7 +1137,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1278,6 +1277,10 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1307,9 +1310,10 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1415,6 +1419,20 @@
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1468,7 +1486,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1610,11 +1627,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="11162256"/>
-        <c:axId val="11159512"/>
+        <c:axId val="301426752"/>
+        <c:axId val="301419304"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11162256"/>
+        <c:axId val="301426752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1646,7 +1663,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1681,7 +1697,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11159512"/>
+        <c:crossAx val="301419304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1689,7 +1705,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11159512"/>
+        <c:axId val="301419304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,7 +1746,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1765,7 +1780,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11162256"/>
+        <c:crossAx val="301426752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1839,7 +1854,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2180,11 +2194,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="11164608"/>
-        <c:axId val="11165000"/>
+        <c:axId val="301425184"/>
+        <c:axId val="301423224"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11164608"/>
+        <c:axId val="301425184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2216,7 +2230,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2251,7 +2264,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11165000"/>
+        <c:crossAx val="301423224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2259,7 +2272,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11165000"/>
+        <c:axId val="301423224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2300,7 +2313,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2335,7 +2347,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11164608"/>
+        <c:crossAx val="301425184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2348,7 +2360,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2601,13 +2612,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
       <sheetData sheetId="8">
         <row r="5">
           <cell r="C5" t="str">
@@ -3539,7 +3550,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3766,7 +3777,7 @@
       <calculatedColumnFormula>L62</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4034,21 +4045,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:B37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" s="71" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" t="s">
         <v>286</v>
       </c>
-      <c r="B3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="72" t="s">
         <v>116</v>
       </c>
@@ -4056,7 +4067,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" s="73" t="s">
         <v>130</v>
       </c>
@@ -4064,7 +4075,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" s="72" t="s">
         <v>17</v>
       </c>
@@ -4072,7 +4083,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" s="73" t="s">
         <v>121</v>
       </c>
@@ -4080,7 +4091,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" s="72" t="s">
         <v>76</v>
       </c>
@@ -4088,7 +4099,7 @@
         <v>780000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" s="73" t="s">
         <v>129</v>
       </c>
@@ -4096,7 +4107,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" s="73" t="s">
         <v>139</v>
       </c>
@@ -4104,7 +4115,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" s="72" t="s">
         <v>55</v>
       </c>
@@ -4112,7 +4123,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" s="73" t="s">
         <v>136</v>
       </c>
@@ -4120,7 +4131,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" s="73" t="s">
         <v>126</v>
       </c>
@@ -4128,7 +4139,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" s="72" t="s">
         <v>21</v>
       </c>
@@ -4136,7 +4147,7 @@
         <v>940000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" s="73" t="s">
         <v>135</v>
       </c>
@@ -4144,7 +4155,7 @@
         <v>470000</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2">
       <c r="A16" s="73" t="s">
         <v>125</v>
       </c>
@@ -4152,7 +4163,7 @@
         <v>470000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" s="72" t="s">
         <v>56</v>
       </c>
@@ -4160,7 +4171,7 @@
         <v>1520000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2">
       <c r="A18" s="73" t="s">
         <v>127</v>
       </c>
@@ -4168,7 +4179,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2">
       <c r="A19" s="73" t="s">
         <v>137</v>
       </c>
@@ -4176,7 +4187,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2">
       <c r="A20" s="73" t="s">
         <v>133</v>
       </c>
@@ -4184,7 +4195,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2">
       <c r="A21" s="72" t="s">
         <v>19</v>
       </c>
@@ -4192,7 +4203,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2">
       <c r="A22" s="73" t="s">
         <v>123</v>
       </c>
@@ -4200,7 +4211,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2">
       <c r="A23" s="72" t="s">
         <v>118</v>
       </c>
@@ -4208,7 +4219,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2">
       <c r="A24" s="73" t="s">
         <v>134</v>
       </c>
@@ -4216,7 +4227,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2">
       <c r="A25" s="72" t="s">
         <v>16</v>
       </c>
@@ -4224,7 +4235,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2">
       <c r="A26" s="73" t="s">
         <v>120</v>
       </c>
@@ -4232,7 +4243,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2">
       <c r="A27" s="72" t="s">
         <v>58</v>
       </c>
@@ -4240,7 +4251,7 @@
         <v>420000</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2">
       <c r="A28" s="73" t="s">
         <v>128</v>
       </c>
@@ -4248,7 +4259,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2">
       <c r="A29" s="73" t="s">
         <v>138</v>
       </c>
@@ -4256,7 +4267,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2">
       <c r="A30" s="72" t="s">
         <v>20</v>
       </c>
@@ -4264,7 +4275,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2">
       <c r="A31" s="73" t="s">
         <v>124</v>
       </c>
@@ -4272,7 +4283,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2">
       <c r="A32" s="72" t="s">
         <v>18</v>
       </c>
@@ -4280,7 +4291,7 @@
         <v>1040000</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2">
       <c r="A33" s="73" t="s">
         <v>132</v>
       </c>
@@ -4288,7 +4299,7 @@
         <v>520000</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2">
       <c r="A34" s="73" t="s">
         <v>122</v>
       </c>
@@ -4296,7 +4307,7 @@
         <v>520000</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2">
       <c r="A35" s="72" t="s">
         <v>117</v>
       </c>
@@ -4304,7 +4315,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2">
       <c r="A36" s="73" t="s">
         <v>131</v>
       </c>
@@ -4312,9 +4323,9 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2">
       <c r="A37" s="72" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B37" s="39">
         <v>6520000</v>
@@ -4328,7 +4339,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.90625" style="2" bestFit="1" customWidth="1"/>
@@ -4339,7 +4350,7 @@
     <col min="9" max="9" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
@@ -4368,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -4400,14 +4411,14 @@
         <v>45660</v>
       </c>
       <c r="J2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K2" s="74">
         <f>MAX(F2:F21)</f>
         <v>600000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -4436,14 +4447,14 @@
         <v>45660</v>
       </c>
       <c r="J3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K3" s="74">
         <f>MIN(F2:F21)</f>
         <v>150000</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -4472,10 +4483,10 @@
         <v>45690</v>
       </c>
       <c r="J4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -4504,10 +4515,10 @@
         <v>46054</v>
       </c>
       <c r="J5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -4536,10 +4547,10 @@
         <v>45728</v>
       </c>
       <c r="J6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -4568,10 +4579,10 @@
         <v>45759</v>
       </c>
       <c r="J7" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -4600,10 +4611,10 @@
         <v>45787</v>
       </c>
       <c r="J8" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -4632,10 +4643,10 @@
         <v>45785</v>
       </c>
       <c r="J9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -4664,10 +4675,10 @@
         <v>45813</v>
       </c>
       <c r="J10" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="3" t="s">
         <v>53</v>
       </c>
@@ -4696,10 +4707,10 @@
         <v>45817</v>
       </c>
       <c r="J11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="3" t="s">
         <v>96</v>
       </c>
@@ -4728,10 +4739,10 @@
         <v>46025</v>
       </c>
       <c r="J12" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="3" t="s">
         <v>97</v>
       </c>
@@ -4760,10 +4771,10 @@
         <v>46025</v>
       </c>
       <c r="J13" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="3" t="s">
         <v>98</v>
       </c>
@@ -4792,10 +4803,10 @@
         <v>46055</v>
       </c>
       <c r="J14" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
         <v>99</v>
       </c>
@@ -4824,10 +4835,10 @@
         <v>46054</v>
       </c>
       <c r="J15" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="3" t="s">
         <v>100</v>
       </c>
@@ -4856,10 +4867,10 @@
         <v>45728</v>
       </c>
       <c r="J16" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
         <v>101</v>
       </c>
@@ -4888,10 +4899,10 @@
         <v>45759</v>
       </c>
       <c r="J17" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
         <v>102</v>
       </c>
@@ -4920,10 +4931,10 @@
         <v>45787</v>
       </c>
       <c r="J18" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
         <v>103</v>
       </c>
@@ -4952,10 +4963,10 @@
         <v>45785</v>
       </c>
       <c r="J19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
         <v>104</v>
       </c>
@@ -4984,10 +4995,10 @@
         <v>45813</v>
       </c>
       <c r="J20" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
         <v>105</v>
       </c>
@@ -5016,7 +5027,7 @@
         <v>45756</v>
       </c>
       <c r="J21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -5028,7 +5039,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
@@ -5043,7 +5054,7 @@
     <col min="11" max="11" width="12.36328125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" s="20" t="s">
         <v>32</v>
       </c>
@@ -5078,7 +5089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -5107,13 +5118,13 @@
         <v>29500</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -5148,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
@@ -5183,7 +5194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>68</v>
       </c>
@@ -5218,7 +5229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>70</v>
       </c>
@@ -5253,7 +5264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -5288,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -5323,7 +5334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -5352,13 +5363,13 @@
         <v>52000</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K9" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>50</v>
       </c>
@@ -5393,7 +5404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>52</v>
       </c>
@@ -5428,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>71</v>
       </c>
@@ -5463,7 +5474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
@@ -5492,13 +5503,13 @@
         <v>61000</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K13" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>73</v>
       </c>
@@ -5533,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
@@ -5568,7 +5579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
@@ -5603,7 +5614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>91</v>
       </c>
@@ -5638,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>92</v>
       </c>
@@ -5667,13 +5678,13 @@
         <v>24000</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K18" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>93</v>
       </c>
@@ -5708,7 +5719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>94</v>
       </c>
@@ -5743,7 +5754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>95</v>
       </c>
@@ -5786,7 +5797,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="12.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
@@ -5796,9 +5807,9 @@
     <col min="7" max="7" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" style="17" customWidth="1"/>
     <col min="11" max="11" width="21.26953125" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.26953125" style="75" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.7265625" style="2"/>
     <col min="15" max="15" width="21.26953125" style="2" bestFit="1" customWidth="1"/>
@@ -5807,7 +5818,7 @@
     <col min="19" max="19" width="22.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21">
       <c r="A1" s="29" t="s">
         <v>31</v>
       </c>
@@ -5835,21 +5846,21 @@
       <c r="I1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="21" t="s">
         <v>36</v>
       </c>
       <c r="K1" s="31" t="s">
         <v>109</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
       <c r="T1" s="8"/>
       <c r="U1" s="8"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
@@ -5878,18 +5889,18 @@
       <c r="I2" s="3">
         <v>3</v>
       </c>
-      <c r="J2" s="4">
-        <v>46297</v>
+      <c r="J2" s="19">
+        <v>45871</v>
       </c>
       <c r="K2" s="11">
         <f>F2*G2*3+F2+H2</f>
         <v>57000</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L2" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -5918,15 +5929,18 @@
       <c r="I3" s="3">
         <v>3</v>
       </c>
-      <c r="J3" s="4">
-        <v>46330</v>
+      <c r="J3" s="19">
+        <v>45903</v>
       </c>
       <c r="K3" s="11">
         <f>F3*G3*3+H3+F3</f>
         <v>81400</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L3" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -5955,15 +5969,18 @@
       <c r="I4" s="3">
         <v>3</v>
       </c>
-      <c r="J4" s="4">
-        <v>46300</v>
+      <c r="J4" s="19">
+        <v>45932</v>
       </c>
       <c r="K4" s="11">
         <f>F2*G2*3+H4+F4</f>
         <v>98000</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L4" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -5992,15 +6009,18 @@
       <c r="I5" s="3">
         <v>3</v>
       </c>
-      <c r="J5" s="4">
-        <v>46301</v>
+      <c r="J5" s="19">
+        <v>45903</v>
       </c>
       <c r="K5" s="11">
         <f t="shared" ref="K5:K21" si="1">F5*G5*I5+H5+F5</f>
         <v>126200</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L5" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -6029,15 +6049,18 @@
       <c r="I6" s="3">
         <v>3</v>
       </c>
-      <c r="J6" s="4">
-        <v>46302</v>
+      <c r="J6" s="19">
+        <v>45933</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
         <v>148600</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L6" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
@@ -6066,15 +6089,18 @@
       <c r="I7" s="3">
         <v>3</v>
       </c>
-      <c r="J7" s="4">
-        <v>46303</v>
+      <c r="J7" s="19">
+        <v>45964</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
         <v>173000</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L7" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
@@ -6103,15 +6129,18 @@
       <c r="I8" s="3">
         <v>3</v>
       </c>
-      <c r="J8" s="4">
-        <v>46304</v>
+      <c r="J8" s="19">
+        <v>45873</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" si="1"/>
         <v>192900</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L8" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -6140,15 +6169,18 @@
       <c r="I9" s="3">
         <v>3</v>
       </c>
-      <c r="J9" s="4">
-        <v>46305</v>
+      <c r="J9" s="19">
+        <v>45904</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="1"/>
         <v>68200</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L9" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>79</v>
       </c>
@@ -6177,15 +6209,18 @@
       <c r="I10" s="3">
         <v>3</v>
       </c>
-      <c r="J10" s="4">
-        <v>46306</v>
+      <c r="J10" s="19">
+        <v>45934</v>
       </c>
       <c r="K10" s="11">
         <f t="shared" si="1"/>
         <v>91600</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L10" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>80</v>
       </c>
@@ -6214,15 +6249,18 @@
       <c r="I11" s="3">
         <v>3</v>
       </c>
-      <c r="J11" s="4">
-        <v>46307</v>
+      <c r="J11" s="19">
+        <v>45937</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="1"/>
         <v>115000</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L11" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>81</v>
       </c>
@@ -6251,19 +6289,18 @@
       <c r="I12" s="3">
         <v>3</v>
       </c>
-      <c r="J12" s="4">
-        <v>46308</v>
+      <c r="J12" s="19">
+        <v>45968</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="1"/>
         <v>137400</v>
       </c>
-      <c r="L12" s="18">
-        <f>K12/I12</f>
-        <v>45800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L12" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="1" t="s">
         <v>82</v>
       </c>
@@ -6292,15 +6329,18 @@
       <c r="I13" s="3">
         <v>3</v>
       </c>
-      <c r="J13" s="4">
-        <v>46309</v>
+      <c r="J13" s="19">
+        <v>45998</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="1"/>
         <v>159800</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L13" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="1" t="s">
         <v>83</v>
       </c>
@@ -6329,15 +6369,18 @@
       <c r="I14" s="3">
         <v>3</v>
       </c>
-      <c r="J14" s="4">
-        <v>46310</v>
+      <c r="J14" s="19">
+        <v>45969</v>
       </c>
       <c r="K14" s="11">
         <f t="shared" si="1"/>
         <v>184200</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L14" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="1" t="s">
         <v>84</v>
       </c>
@@ -6366,15 +6409,18 @@
       <c r="I15" s="3">
         <v>3</v>
       </c>
-      <c r="J15" s="4">
-        <v>46311</v>
+      <c r="J15" s="19">
+        <v>45999</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
         <v>206600</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="L15" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="1" t="s">
         <v>85</v>
       </c>
@@ -6403,18 +6449,18 @@
       <c r="I16" s="3">
         <v>3</v>
       </c>
-      <c r="J16" s="4">
-        <v>46312</v>
+      <c r="J16" s="19">
+        <v>46030</v>
       </c>
       <c r="K16" s="11">
         <f t="shared" si="1"/>
         <v>229000</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L16" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
         <v>86</v>
       </c>
@@ -6443,15 +6489,18 @@
       <c r="I17" s="3">
         <v>3</v>
       </c>
-      <c r="J17" s="4">
-        <v>46313</v>
+      <c r="J17" s="19">
+        <v>45878</v>
       </c>
       <c r="K17" s="11">
         <f t="shared" si="1"/>
         <v>80400</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L17" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
         <v>87</v>
       </c>
@@ -6480,15 +6529,18 @@
       <c r="I18" s="3">
         <v>3</v>
       </c>
-      <c r="J18" s="4">
-        <v>46314</v>
+      <c r="J18" s="19">
+        <v>45909</v>
       </c>
       <c r="K18" s="11">
         <f t="shared" si="1"/>
         <v>102800</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L18" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
         <v>88</v>
       </c>
@@ -6517,15 +6569,18 @@
       <c r="I19" s="3">
         <v>3</v>
       </c>
-      <c r="J19" s="4">
-        <v>46315</v>
+      <c r="J19" s="19">
+        <v>45939</v>
       </c>
       <c r="K19" s="11">
         <f t="shared" si="1"/>
         <v>126200</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L19" s="75" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
         <v>89</v>
       </c>
@@ -6554,15 +6609,18 @@
       <c r="I20" s="3">
         <v>3</v>
       </c>
-      <c r="J20" s="4">
-        <v>46316</v>
+      <c r="J20" s="19">
+        <v>45879</v>
       </c>
       <c r="K20" s="11">
         <f t="shared" si="1"/>
         <v>57000</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L20" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
         <v>90</v>
       </c>
@@ -6591,18 +6649,23 @@
       <c r="I21" s="3">
         <v>3</v>
       </c>
-      <c r="J21" s="4">
-        <v>46317</v>
+      <c r="J21" s="19">
+        <v>45910</v>
       </c>
       <c r="K21" s="11">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L21" s="75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="J22" s="19"/>
+      <c r="L22" s="76"/>
       <c r="P22"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16">
       <c r="A23" s="28"/>
       <c r="B23"/>
       <c r="C23" s="12"/>
@@ -6610,178 +6673,166 @@
       <c r="G23" s="12"/>
       <c r="H23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23"/>
+      <c r="L23" s="76"/>
       <c r="M23"/>
       <c r="N23"/>
       <c r="O23"/>
       <c r="P23"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16">
       <c r="A24" s="28"/>
       <c r="B24"/>
       <c r="C24" s="12"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="J24"/>
       <c r="K24"/>
-      <c r="L24"/>
+      <c r="L24" s="76"/>
       <c r="M24"/>
       <c r="N24"/>
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16">
       <c r="A25" s="28"/>
       <c r="B25"/>
       <c r="C25" s="12"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="J25"/>
       <c r="K25"/>
-      <c r="L25"/>
+      <c r="L25" s="76"/>
       <c r="M25"/>
       <c r="N25"/>
       <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16">
       <c r="A26" s="28"/>
       <c r="B26"/>
       <c r="C26" s="12"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="J26"/>
       <c r="K26"/>
-      <c r="L26"/>
+      <c r="L26" s="76"/>
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26"/>
       <c r="P26"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16">
       <c r="A27" s="28"/>
       <c r="B27"/>
       <c r="C27" s="12"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="J27"/>
       <c r="K27"/>
-      <c r="L27"/>
+      <c r="L27" s="76"/>
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27"/>
       <c r="P27"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16">
       <c r="A28" s="28"/>
       <c r="B28"/>
       <c r="C28" s="12"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="J28"/>
       <c r="K28"/>
-      <c r="L28"/>
+      <c r="L28" s="76"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
       <c r="P28"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16">
       <c r="A29" s="28"/>
       <c r="B29"/>
       <c r="C29" s="12"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="J29"/>
       <c r="K29"/>
-      <c r="L29"/>
+      <c r="L29" s="76"/>
       <c r="M29"/>
       <c r="N29"/>
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16">
       <c r="A30" s="28"/>
       <c r="B30"/>
       <c r="C30" s="12"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="J30"/>
       <c r="K30"/>
-      <c r="L30"/>
+      <c r="L30" s="76"/>
       <c r="M30"/>
       <c r="N30"/>
       <c r="O30"/>
       <c r="P30"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16">
       <c r="A31" s="28"/>
       <c r="B31"/>
       <c r="C31" s="12"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="J31"/>
       <c r="K31"/>
-      <c r="L31"/>
+      <c r="L31" s="76"/>
       <c r="M31"/>
       <c r="N31"/>
       <c r="O31"/>
       <c r="P31"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16">
       <c r="A32" s="28"/>
       <c r="B32"/>
       <c r="C32" s="12"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="J32"/>
       <c r="K32"/>
-      <c r="L32"/>
+      <c r="L32" s="76"/>
       <c r="M32"/>
       <c r="N32"/>
       <c r="O32"/>
       <c r="P32"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16">
       <c r="A33" s="28"/>
       <c r="B33"/>
       <c r="C33" s="12"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="J33"/>
       <c r="K33"/>
-      <c r="L33"/>
+      <c r="L33" s="76"/>
       <c r="M33"/>
       <c r="N33"/>
       <c r="O33"/>
       <c r="P33"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16">
       <c r="A34" s="28"/>
       <c r="B34"/>
       <c r="C34" s="12"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="J34"/>
       <c r="K34"/>
-      <c r="L34"/>
       <c r="M34"/>
       <c r="N34"/>
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16">
       <c r="A35" s="28"/>
       <c r="B35"/>
       <c r="C35" s="12"/>
@@ -6794,7 +6845,7 @@
       <c r="O35"/>
       <c r="P35"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16">
       <c r="A36" s="28"/>
       <c r="B36"/>
       <c r="C36" s="12"/>
@@ -6807,7 +6858,7 @@
       <c r="O36"/>
       <c r="P36"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16">
       <c r="A37" s="28"/>
       <c r="B37"/>
       <c r="C37" s="12"/>
@@ -6820,7 +6871,7 @@
       <c r="O37"/>
       <c r="P37"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16">
       <c r="A38" s="28"/>
       <c r="B38"/>
       <c r="C38" s="12"/>
@@ -6833,7 +6884,7 @@
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16">
       <c r="A39" s="28"/>
       <c r="B39"/>
       <c r="C39" s="12"/>
@@ -6846,7 +6897,7 @@
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16">
       <c r="A40" s="28"/>
       <c r="B40"/>
       <c r="C40" s="12"/>
@@ -6859,7 +6910,7 @@
       <c r="O40"/>
       <c r="P40"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16">
       <c r="A41" s="28"/>
       <c r="B41"/>
       <c r="C41" s="12"/>
@@ -6872,7 +6923,7 @@
       <c r="O41"/>
       <c r="P41"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16">
       <c r="A42" s="28"/>
       <c r="B42"/>
       <c r="C42" s="12"/>
@@ -6885,7 +6936,7 @@
       <c r="O42"/>
       <c r="P42"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16">
       <c r="A43" s="28"/>
       <c r="B43"/>
       <c r="C43" s="12"/>
@@ -6898,7 +6949,7 @@
       <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16">
       <c r="A44" s="28"/>
       <c r="B44"/>
       <c r="C44" s="12"/>
@@ -6911,7 +6962,7 @@
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16">
       <c r="A45" s="28"/>
       <c r="B45"/>
       <c r="C45" s="12"/>
@@ -6924,7 +6975,7 @@
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16">
       <c r="A46" s="28"/>
       <c r="B46"/>
       <c r="C46" s="12"/>
@@ -6937,7 +6988,7 @@
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16">
       <c r="A47" s="28"/>
       <c r="B47"/>
       <c r="C47" s="12"/>
@@ -6950,7 +7001,7 @@
       <c r="O47"/>
       <c r="P47"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16">
       <c r="A48" s="28"/>
       <c r="B48"/>
       <c r="C48" s="12"/>
@@ -6963,7 +7014,7 @@
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16">
       <c r="A49" s="28"/>
       <c r="B49"/>
       <c r="C49" s="12"/>
@@ -6976,10 +7027,18 @@
       <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16">
       <c r="A50" s="28"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="closed">
+      <formula>NOT(ISERROR(SEARCH("closed",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="Active">
+      <formula>NOT(ISERROR(SEARCH("Active",L1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6988,7 +7047,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.08984375" style="2" customWidth="1"/>
@@ -7003,10 +7062,11 @@
     <col min="11" max="11" width="27.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23" style="2" customWidth="1"/>
     <col min="13" max="13" width="10.08984375" style="37" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15">
       <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
@@ -7023,13 +7083,13 @@
         <v>78</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I1" s="25" t="s">
         <v>114</v>
@@ -7038,7 +7098,7 @@
         <v>115</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L1" s="26" t="s">
         <v>111</v>
@@ -7049,11 +7109,11 @@
       <c r="N1" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="O1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O1" s="77" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
@@ -7071,7 +7131,7 @@
         <v>45871</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G2" s="12">
         <f t="shared" ref="G2:G7" si="0">D2</f>
@@ -7104,11 +7164,11 @@
         <f>IF(M2="","Current",IF(M2&lt;=0,"Current",IF(M2&lt;=7,"1–7",IF(M2&lt;=30,"8–30",IF(M2&lt;=60,"31–60",IF(M2&lt;=90,"61–90","90+"))))))</f>
         <v>Current</v>
       </c>
-      <c r="O2" s="17">
+      <c r="O2" s="7">
         <v>45969</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>37</v>
       </c>
@@ -7126,7 +7186,7 @@
         <v>45902</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G3" s="12">
         <f t="shared" si="0"/>
@@ -7159,11 +7219,11 @@
         <f t="shared" ref="N3:N64" si="1">IF(M3="","Current",IF(M3&lt;=0,"Current",IF(M3&lt;=7,"1–7",IF(M3&lt;=30,"8–30",IF(M3&lt;=60,"31–60",IF(M3&lt;=90,"61–90","90+"))))))</f>
         <v>Current</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="7">
         <v>45970</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -7181,7 +7241,7 @@
         <v>45932</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" si="0"/>
@@ -7214,11 +7274,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="7">
         <v>45971</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
@@ -7236,7 +7296,7 @@
         <v>45903</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G5" s="12">
         <f t="shared" si="0"/>
@@ -7269,11 +7329,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="7">
         <v>45972</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
@@ -7291,7 +7351,7 @@
         <v>45933</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" si="0"/>
@@ -7324,11 +7384,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="7">
         <v>45973</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
@@ -7346,7 +7406,7 @@
         <v>45964</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" si="0"/>
@@ -7379,11 +7439,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="7">
         <v>45974</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15">
       <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
@@ -7401,7 +7461,7 @@
         <v>45873</v>
       </c>
       <c r="F8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G8" s="12">
         <v>13000</v>
@@ -7430,11 +7490,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="7">
         <v>45975</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15">
       <c r="A9" s="14" t="s">
         <v>41</v>
       </c>
@@ -7452,7 +7512,7 @@
         <v>45904</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G9" s="12">
         <v>10000</v>
@@ -7481,11 +7541,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="7">
         <v>45976</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15">
       <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
@@ -7503,7 +7563,7 @@
         <v>45934</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G10" s="12">
         <v>14000</v>
@@ -7532,11 +7592,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="7">
         <v>45977</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -7551,10 +7611,10 @@
         <v>42066.666666666664</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G11" s="12">
         <v>0</v>
@@ -7583,11 +7643,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O11" s="17">
-        <v>45978</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O11" s="7">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -7602,10 +7662,10 @@
         <v>42066.666666666664</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G12" s="12">
         <v>0</v>
@@ -7634,11 +7694,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="7">
         <v>45979</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
@@ -7653,10 +7713,10 @@
         <v>42066.666666666664</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
@@ -7685,11 +7745,11 @@
         <f t="shared" si="1"/>
         <v>31–60</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="7">
         <v>45980</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
@@ -7707,7 +7767,7 @@
         <v>45938</v>
       </c>
       <c r="F14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G14" s="12">
         <f>D14</f>
@@ -7737,11 +7797,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="7">
         <v>45981</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -7759,7 +7819,7 @@
         <v>45969</v>
       </c>
       <c r="F15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G15" s="12">
         <f>D15</f>
@@ -7789,11 +7849,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="7">
         <v>45982</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
@@ -7811,7 +7871,7 @@
         <v>45999</v>
       </c>
       <c r="F16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G16" s="12">
         <f>D16</f>
@@ -7841,11 +7901,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="7">
         <v>45983</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15">
       <c r="A17" s="3" t="s">
         <v>47</v>
       </c>
@@ -7860,10 +7920,10 @@
         <v>57666.666666666664</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
@@ -7892,11 +7952,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="7">
         <v>45984</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15">
       <c r="A18" s="3" t="s">
         <v>47</v>
       </c>
@@ -7914,7 +7974,7 @@
         <v>45909</v>
       </c>
       <c r="F18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G18" s="12">
         <f>H17+D18</f>
@@ -7944,11 +8004,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O18" s="17">
+      <c r="O18" s="7">
         <v>45985</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15">
       <c r="A19" s="3" t="s">
         <v>47</v>
       </c>
@@ -7966,7 +8026,7 @@
         <v>46000</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G19" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -7992,11 +8052,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="7">
         <v>45986</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
         <v>49</v>
       </c>
@@ -8014,7 +8074,7 @@
         <v>45879</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G20" s="12">
         <f>D20</f>
@@ -8047,11 +8107,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="7">
         <v>45987</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
         <v>49</v>
       </c>
@@ -8069,7 +8129,7 @@
         <v>45910</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G21" s="12">
         <f>D21</f>
@@ -8102,11 +8162,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="7">
         <v>45988</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15">
       <c r="A22" s="3" t="s">
         <v>49</v>
       </c>
@@ -8124,7 +8184,7 @@
         <v>45940</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G22" s="12">
         <f>D22</f>
@@ -8157,11 +8217,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="7">
         <v>45989</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15">
       <c r="A23" s="3" t="s">
         <v>51</v>
       </c>
@@ -8179,7 +8239,7 @@
         <v>45972</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G23" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8209,11 +8269,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="7">
         <v>46050</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15">
       <c r="A24" s="3" t="s">
         <v>51</v>
       </c>
@@ -8231,7 +8291,7 @@
         <v>46002</v>
       </c>
       <c r="F24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G24" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8261,11 +8321,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="7">
         <v>45991</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15">
       <c r="A25" s="3" t="s">
         <v>51</v>
       </c>
@@ -8283,7 +8343,7 @@
         <v>46033</v>
       </c>
       <c r="F25" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G25" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8313,11 +8373,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="7">
         <v>45992</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15">
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
@@ -8335,7 +8395,7 @@
         <v>45881</v>
       </c>
       <c r="F26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G26" s="12">
         <v>12000</v>
@@ -8364,11 +8424,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="7">
         <v>45993</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15">
       <c r="A27" s="3" t="s">
         <v>79</v>
       </c>
@@ -8386,7 +8446,7 @@
         <v>46003</v>
       </c>
       <c r="F27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G27" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8413,11 +8473,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="7">
         <v>45994</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15">
       <c r="A28" s="3" t="s">
         <v>79</v>
       </c>
@@ -8435,7 +8495,7 @@
         <v>46065</v>
       </c>
       <c r="F28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G28" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8462,11 +8522,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="7">
         <v>45995</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15">
       <c r="A29" s="3" t="s">
         <v>80</v>
       </c>
@@ -8481,10 +8541,10 @@
         <v>38333.333333333336</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
@@ -8513,11 +8573,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="7">
         <v>45996</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15">
       <c r="A30" s="3" t="s">
         <v>80</v>
       </c>
@@ -8532,10 +8592,10 @@
         <v>38333.333333333336</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G30" s="12">
         <v>0</v>
@@ -8564,11 +8624,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="7">
         <v>45997</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15">
       <c r="A31" s="3" t="s">
         <v>80</v>
       </c>
@@ -8583,10 +8643,10 @@
         <v>38333.333333333336</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G31" s="12">
         <v>0</v>
@@ -8615,11 +8675,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="7">
         <v>45998</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15">
       <c r="A32" s="3" t="s">
         <v>81</v>
       </c>
@@ -8637,7 +8697,7 @@
         <v>45874</v>
       </c>
       <c r="F32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G32" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8667,11 +8727,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O32" s="17">
+      <c r="O32" s="7">
         <v>45999</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15">
       <c r="A33" s="3" t="s">
         <v>81</v>
       </c>
@@ -8689,7 +8749,7 @@
         <v>45901</v>
       </c>
       <c r="F33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G33" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8719,13 +8779,13 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O33" s="17">
+      <c r="O33" s="7">
         <v>46000</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15">
       <c r="A34" s="3" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3">
         <v>3</v>
@@ -8741,7 +8801,7 @@
         <v>45930</v>
       </c>
       <c r="F34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G34" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8771,11 +8831,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O34" s="17">
+      <c r="O34" s="7">
         <v>46001</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
@@ -8790,10 +8850,10 @@
         <v>53266.666666666664</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G35" s="12">
         <v>0</v>
@@ -8822,11 +8882,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O35" s="17">
+      <c r="O35" s="7">
         <v>46002</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15">
       <c r="A36" s="3" t="s">
         <v>82</v>
       </c>
@@ -8844,7 +8904,7 @@
         <v>45915</v>
       </c>
       <c r="F36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G36" s="12">
         <f>H35+D37</f>
@@ -8874,11 +8934,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O36" s="17">
+      <c r="O36" s="7">
         <v>46003</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15">
       <c r="A37" s="3" t="s">
         <v>82</v>
       </c>
@@ -8896,7 +8956,7 @@
         <v>46006</v>
       </c>
       <c r="F37" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G37" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8926,11 +8986,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O37" s="17">
+      <c r="O37" s="7">
         <v>46004</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15">
       <c r="A38" s="3" t="s">
         <v>83</v>
       </c>
@@ -8948,7 +9008,7 @@
         <v>45885</v>
       </c>
       <c r="F38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G38" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -8981,11 +9041,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O38" s="17">
+      <c r="O38" s="7">
         <v>46005</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15">
       <c r="A39" s="3" t="s">
         <v>83</v>
       </c>
@@ -9003,7 +9063,7 @@
         <v>45916</v>
       </c>
       <c r="F39" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G39" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9036,11 +9096,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O39" s="17">
+      <c r="O39" s="7">
         <v>46006</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15">
       <c r="A40" s="3" t="s">
         <v>83</v>
       </c>
@@ -9058,7 +9118,7 @@
         <v>45946</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G40" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9091,11 +9151,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O40" s="17">
+      <c r="O40" s="7">
         <v>46007</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15">
       <c r="A41" s="3" t="s">
         <v>84</v>
       </c>
@@ -9113,7 +9173,7 @@
         <v>45937</v>
       </c>
       <c r="F41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G41" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9143,11 +9203,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O41" s="17">
+      <c r="O41" s="7">
         <v>46008</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15">
       <c r="A42" s="3" t="s">
         <v>84</v>
       </c>
@@ -9165,7 +9225,7 @@
         <v>45984</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G42" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9195,11 +9255,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O42" s="17">
+      <c r="O42" s="7">
         <v>46009</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -9217,7 +9277,7 @@
         <v>46018</v>
       </c>
       <c r="F43" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G43" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9247,11 +9307,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O43" s="17">
+      <c r="O43" s="7">
         <v>46010</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15">
       <c r="A44" s="3" t="s">
         <v>85</v>
       </c>
@@ -9269,7 +9329,7 @@
         <v>45887</v>
       </c>
       <c r="F44" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G44" s="12"/>
       <c r="I44" s="12">
@@ -9286,11 +9346,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="7">
         <v>46011</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15">
       <c r="A45" s="3" t="s">
         <v>85</v>
       </c>
@@ -9308,7 +9368,7 @@
         <v>45918</v>
       </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G45" s="12"/>
       <c r="I45" s="12">
@@ -9325,11 +9385,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O45" s="17">
+      <c r="O45" s="7">
         <v>46012</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15">
       <c r="A46" s="3" t="s">
         <v>85</v>
       </c>
@@ -9347,7 +9407,7 @@
         <v>45948</v>
       </c>
       <c r="F46" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G46" s="12"/>
       <c r="I46" s="12">
@@ -9364,11 +9424,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="7">
         <v>46013</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15">
       <c r="A47" s="3" t="s">
         <v>86</v>
       </c>
@@ -9386,7 +9446,7 @@
         <v>45888</v>
       </c>
       <c r="F47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G47" s="12"/>
       <c r="I47" s="12">
@@ -9403,11 +9463,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O47" s="17">
+      <c r="O47" s="7">
         <v>46014</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15">
       <c r="A48" s="3" t="s">
         <v>86</v>
       </c>
@@ -9425,7 +9485,7 @@
         <v>45919</v>
       </c>
       <c r="F48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G48" s="12"/>
       <c r="I48" s="12">
@@ -9442,13 +9502,13 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O48" s="17">
+      <c r="O48" s="7">
         <v>46015</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15">
       <c r="A49" s="3" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="B49" s="3">
         <v>3</v>
@@ -9464,12 +9524,12 @@
         <v>45949</v>
       </c>
       <c r="F49" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G49" s="12"/>
       <c r="I49" s="12">
         <f t="shared" si="4"/>
-        <v>26800</v>
+        <v>80400</v>
       </c>
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
@@ -9481,11 +9541,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O49" s="17">
+      <c r="O49" s="7">
         <v>46016</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15">
       <c r="A50" s="3" t="s">
         <v>87</v>
       </c>
@@ -9503,7 +9563,7 @@
         <v>45874</v>
       </c>
       <c r="F50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G50" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9533,11 +9593,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O50" s="17">
+      <c r="O50" s="7">
         <v>46017</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15">
       <c r="A51" s="3" t="s">
         <v>87</v>
       </c>
@@ -9555,7 +9615,7 @@
         <v>45901</v>
       </c>
       <c r="F51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G51" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9585,11 +9645,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O51" s="17">
+      <c r="O51" s="7">
         <v>46018</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15">
       <c r="A52" s="3" t="s">
         <v>87</v>
       </c>
@@ -9607,7 +9667,7 @@
         <v>45931</v>
       </c>
       <c r="F52" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G52" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9637,11 +9697,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O52" s="17">
+      <c r="O52" s="7">
         <v>46019</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15">
       <c r="A53" s="3" t="s">
         <v>88</v>
       </c>
@@ -9659,7 +9719,7 @@
         <v>45890</v>
       </c>
       <c r="F53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G53" s="12"/>
       <c r="I53" s="12">
@@ -9676,11 +9736,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O53" s="17">
+      <c r="O53" s="7">
         <v>46020</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15">
       <c r="A54" s="3" t="s">
         <v>88</v>
       </c>
@@ -9698,7 +9758,7 @@
         <v>45921</v>
       </c>
       <c r="F54" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G54" s="12"/>
       <c r="I54" s="12">
@@ -9715,11 +9775,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O54" s="17">
+      <c r="O54" s="7">
         <v>46021</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15">
       <c r="A55" s="3" t="s">
         <v>88</v>
       </c>
@@ -9737,7 +9797,7 @@
         <v>45951</v>
       </c>
       <c r="F55" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G55" s="12"/>
       <c r="I55" s="12">
@@ -9754,11 +9814,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O55" s="17">
+      <c r="O55" s="7">
         <v>46022</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15">
       <c r="A56" s="3" t="s">
         <v>89</v>
       </c>
@@ -9776,7 +9836,7 @@
         <v>45891</v>
       </c>
       <c r="F56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G56" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9809,11 +9869,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O56" s="17">
+      <c r="O56" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15">
       <c r="A57" s="3" t="s">
         <v>89</v>
       </c>
@@ -9831,7 +9891,7 @@
         <v>45922</v>
       </c>
       <c r="F57" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G57" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9864,11 +9924,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O57" s="17">
+      <c r="O57" s="7">
         <v>46024</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15">
       <c r="A58" s="3" t="s">
         <v>89</v>
       </c>
@@ -9886,7 +9946,7 @@
         <v>45952</v>
       </c>
       <c r="F58" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G58" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9919,11 +9979,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O58" s="17">
+      <c r="O58" s="7">
         <v>46025</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15">
       <c r="A59" s="3" t="s">
         <v>90</v>
       </c>
@@ -9941,7 +10001,7 @@
         <v>45892</v>
       </c>
       <c r="F59" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G59" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -9967,11 +10027,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O59" s="17">
+      <c r="O59" s="7">
         <v>46026</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15">
       <c r="A60" s="3" t="s">
         <v>90</v>
       </c>
@@ -9989,7 +10049,7 @@
         <v>45923</v>
       </c>
       <c r="F60" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G60" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -10015,11 +10075,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O60" s="17">
+      <c r="O60" s="7">
         <v>46027</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15">
       <c r="A61" s="3" t="s">
         <v>90</v>
       </c>
@@ -10037,7 +10097,7 @@
         <v>45953</v>
       </c>
       <c r="F61" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G61" s="12">
         <f>Table1[[#This Row],[amount_due]]</f>
@@ -10063,11 +10123,11 @@
         <f t="shared" si="1"/>
         <v>90+</v>
       </c>
-      <c r="O61" s="17">
+      <c r="O61" s="7">
         <v>46028</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15">
       <c r="A62" s="3"/>
       <c r="G62" s="12"/>
       <c r="I62" s="12">
@@ -10084,11 +10144,11 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O62" s="17">
+      <c r="O62" s="7">
         <v>46029</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="19"/>
@@ -10104,12 +10164,12 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O63" s="39">
+      <c r="O63" s="78">
         <f>L123</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="19"/>
@@ -10125,14 +10185,14 @@
         <f t="shared" si="1"/>
         <v>Current</v>
       </c>
-      <c r="O64" s="39">
+      <c r="O64" s="78">
         <f>L124</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="11:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="11:12">
       <c r="K66" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L66" s="7">
         <v>46050</v>
@@ -10150,135 +10210,135 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="84.54296875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="35" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="B2" s="33" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="s">
+      <c r="C2" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="B2" s="33" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="B3" s="33" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="s">
+      <c r="C3" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="33" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="B4" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="33" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="32" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C4" s="33" t="s">
+      <c r="B5" s="33" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="32" t="s">
+      <c r="C5" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="33" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="B6" s="33" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+      <c r="C6" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="33" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="B7" s="33" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="32" t="s">
+      <c r="C7" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="33" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="B8" s="33" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="32" t="s">
+      <c r="C8" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="33" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="B9" s="33" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="32" t="s">
+      <c r="C9" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="32" t="s">
         <v>112</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="32" t="s">
         <v>113</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="B12"/>
       <c r="C12"/>
     </row>
@@ -10290,198 +10350,198 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" style="2" customWidth="1"/>
     <col min="2" max="2" width="82.26953125" style="46" customWidth="1"/>
     <col min="3" max="3" width="52.1796875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="40" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="26">
+      <c r="A2" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="C2" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="42" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="26">
+      <c r="A3" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="B3" s="42" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="s">
+      <c r="C3" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="B3" s="42" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="38.5">
+      <c r="A4" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="B4" s="42" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="s">
+      <c r="C4" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="42" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="38.5">
+      <c r="A5" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="B5" s="42" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="41" t="s">
+      <c r="C5" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="42" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="26">
+      <c r="A6" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="B6" s="42" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A6" s="41" t="s">
+      <c r="C6" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="42" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="26">
+      <c r="A7" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="B7" s="42" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A7" s="41" t="s">
+      <c r="C7" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="42" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="B8" s="42" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="41" t="s">
+      <c r="C8" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="B8" s="42" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="B9" s="42" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="41" t="s">
+      <c r="C9" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" ht="26">
       <c r="A10" s="41" t="s">
         <v>111</v>
       </c>
       <c r="B10" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="B11" s="42" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
+      <c r="C11" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="42" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="B12" s="42" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="41" t="s">
+      <c r="C12" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="42" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="B13" s="42" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="41" t="s">
+      <c r="C13" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="42" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="26">
+      <c r="A14" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="B14" s="42" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="B14" s="42" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="38.5">
+      <c r="A15" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="B15" s="42" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="41" t="s">
+      <c r="C15" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="B15" s="42" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="B16" s="42" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="41" t="s">
+      <c r="C16" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="B16" s="42" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="38.5">
+      <c r="A17" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="B17" s="42" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="C17" s="45" t="s">
         <v>234</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -10492,27 +10552,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7265625" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.36328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>238</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>240</v>
       </c>
       <c r="B2" s="2">
         <v>20</v>
@@ -10521,9 +10581,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B3" s="2">
         <v>60</v>
@@ -10532,9 +10592,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="26">
       <c r="A4" s="45" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B4" s="12">
         <f>SUM(Loan!F2:F21)</f>
@@ -10545,22 +10605,22 @@
         <v>2205000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="26">
       <c r="A5" s="45" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C5" s="12">
         <f>SUM(Loan!K2:K21)</f>
         <v>2520300</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="26">
       <c r="A6" s="45" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C6" s="12">
         <f>SUM(Installment!I33:I61)</f>
-        <v>2637400</v>
+        <v>2691000</v>
       </c>
     </row>
   </sheetData>
@@ -10571,7 +10631,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U46"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="3" style="47" customWidth="1"/>
     <col min="2" max="15" width="15" style="47" customWidth="1"/>
@@ -10579,239 +10639,239 @@
     <col min="21" max="21" width="1" style="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:21" ht="15" customHeight="1">
       <c r="U1" s="48"/>
     </row>
-    <row r="2" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:21" ht="24" customHeight="1">
       <c r="B2" s="49" t="s">
+        <v>243</v>
+      </c>
+      <c r="U2" s="48"/>
+    </row>
+    <row r="3" spans="2:21" ht="13.5" customHeight="1">
+      <c r="B3" s="50" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="15" customHeight="1">
+      <c r="B5" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="U2" s="48"/>
-    </row>
-    <row r="3" spans="2:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="50" t="s">
+    </row>
+    <row r="6" spans="2:21" ht="15" customHeight="1">
+      <c r="B6" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="85">
+        <v>46050</v>
+      </c>
+      <c r="D6" s="85"/>
+      <c r="F6" s="86" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="51" t="s">
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
+    </row>
+    <row r="7" spans="2:21" ht="15" customHeight="1">
+      <c r="B7" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="87" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="81">
-        <v>46050</v>
-      </c>
-      <c r="D6" s="81"/>
-      <c r="F6" s="82" t="s">
+      <c r="D7" s="87"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
+    </row>
+    <row r="8" spans="2:21" ht="15" customHeight="1">
+      <c r="B8" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="87"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+    </row>
+    <row r="9" spans="2:21" ht="15" customHeight="1">
+      <c r="B9" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="87" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="87"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+    </row>
+    <row r="11" spans="2:21" ht="15" customHeight="1">
+      <c r="B11" s="51" t="s">
         <v>248</v>
       </c>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-    </row>
-    <row r="7" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" s="83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D7" s="83"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-    </row>
-    <row r="8" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D8" s="83"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-    </row>
-    <row r="9" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="52" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D9" s="83"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-    </row>
-    <row r="11" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="51" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:21" ht="15" customHeight="1">
       <c r="B12" s="50" t="str">
         <f>"As of "&amp;TEXT($C$6,"dd mmm yyyy")&amp;"  |  Product: "&amp;$C$7&amp;"  |  Channel: "&amp;$C$8&amp;"  |  Customer Type: "&amp;$C$9</f>
         <v>As of 28 Jan 2026  |  Product: All  |  Channel: All  |  Customer Type: All</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="77" t="s">
-        <v>193</v>
-      </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77" t="s">
-        <v>199</v>
-      </c>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77" t="s">
-        <v>202</v>
-      </c>
-      <c r="L13" s="77"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="77" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="77"/>
-      <c r="P13" s="77"/>
-      <c r="Q13" s="77" t="s">
-        <v>208</v>
-      </c>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-    </row>
-    <row r="14" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="78">
+    <row r="13" spans="2:21" ht="15" customHeight="1">
+      <c r="B13" s="81" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81" t="s">
+        <v>206</v>
+      </c>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+    </row>
+    <row r="14" spans="2:21" ht="15" customHeight="1">
+      <c r="B14" s="82">
         <v>20</v>
       </c>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78">
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*('[1]Calc - Loan Summary'!$O$5:$O$24&gt;0)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="79">
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="83">
         <f>SUM(Installment!H8:H61)</f>
         <v>431666.66666666657</v>
       </c>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79">
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83">
         <f>SUM(Installment!D2:D61)</f>
         <v>2520299.9999999995</v>
       </c>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79">
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83">
         <f>SUM(Installment!J2:J61)</f>
         <v>3416466.666666667</v>
       </c>
-      <c r="O14" s="79"/>
-      <c r="P14" s="79"/>
-      <c r="Q14" s="80">
+      <c r="O14" s="83"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="84">
         <f>IFERROR(N14/K14,0)</f>
         <v>1.3555793622452357</v>
       </c>
-      <c r="R14" s="80"/>
-      <c r="S14" s="80"/>
-    </row>
-    <row r="15" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="79"/>
-      <c r="P15" s="79"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
-      <c r="S15" s="80"/>
-    </row>
-    <row r="16" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="80"/>
-      <c r="R16" s="80"/>
-      <c r="S16" s="80"/>
-    </row>
-    <row r="18" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
+    </row>
+    <row r="15" spans="2:21" ht="15" customHeight="1">
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+    </row>
+    <row r="16" spans="2:21" ht="15" customHeight="1">
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="83"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+    </row>
+    <row r="18" spans="2:7" ht="15" customHeight="1">
       <c r="B18" s="51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="34.5" customHeight="1">
+      <c r="B19" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="D19" s="53" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" s="53" t="s">
+      <c r="E19" s="53" t="s">
         <v>252</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="F19" s="53" t="s">
         <v>253</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="G19" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="F19" s="53" t="s">
+    </row>
+    <row r="20" spans="2:7" ht="15" customHeight="1">
+      <c r="B20" s="54" t="s">
         <v>255</v>
-      </c>
-      <c r="G19" s="53" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="54" t="s">
-        <v>257</v>
       </c>
       <c r="C20" s="55">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20))</f>
@@ -10834,9 +10894,9 @@
         <v>5.2821056975290308E-16</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" ht="15" customHeight="1">
       <c r="B21" s="54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C21" s="55">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21))</f>
@@ -10859,9 +10919,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" ht="15" customHeight="1">
       <c r="B22" s="54" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C22" s="55">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22))</f>
@@ -10884,9 +10944,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" ht="15" customHeight="1">
       <c r="B23" s="54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C23" s="55">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23))</f>
@@ -10909,9 +10969,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="15" customHeight="1">
       <c r="B24" s="58" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C24" s="59">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24))</f>
@@ -10934,9 +10994,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:7" ht="15" customHeight="1">
       <c r="B25" s="58" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C25" s="59">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B25))</f>
@@ -10959,9 +11019,9 @@
         <v>0.62518708432683279</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:7" ht="15" customHeight="1">
       <c r="B26" s="62" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C26" s="62">
         <f>SUM(C20:C25)</f>
@@ -10984,14 +11044,14 @@
         <v>0.62518708432683334</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:7" ht="15" customHeight="1">
       <c r="B28" s="51" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="23.25" customHeight="1">
       <c r="B29" s="53" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C29" s="53" t="s">
         <v>69</v>
@@ -11003,12 +11063,12 @@
         <v>67</v>
       </c>
       <c r="F29" s="53" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="15" customHeight="1">
+      <c r="B30" s="54" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="54" t="s">
-        <v>265</v>
       </c>
       <c r="C30" s="57">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
@@ -11027,9 +11087,9 @@
         <v>1895000</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:7" ht="15" customHeight="1">
       <c r="B31" s="54" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C31" s="57">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
@@ -11048,9 +11108,9 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:7" ht="15" customHeight="1">
       <c r="B32" s="54" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C32" s="57">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
@@ -11069,9 +11129,9 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" ht="15" customHeight="1">
       <c r="B33" s="54" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C33" s="57">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
@@ -11090,9 +11150,9 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="34" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:15" ht="15" customHeight="1">
       <c r="B34" s="62" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C34" s="64">
         <f>SUM(C30:C33)</f>
@@ -11111,170 +11171,170 @@
         <v>2205000</v>
       </c>
     </row>
-    <row r="35" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="15" customHeight="1">
       <c r="B35" s="66" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" ht="15" customHeight="1">
+      <c r="B37" s="51" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" ht="18" customHeight="1">
+      <c r="B38" s="80" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="51" t="s">
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+    </row>
+    <row r="39" spans="2:15" ht="84.75" customHeight="1">
+      <c r="B39" s="79" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="76" t="s">
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79"/>
+      <c r="N39" s="79"/>
+      <c r="O39" s="79"/>
+    </row>
+    <row r="40" spans="2:15" ht="18" customHeight="1">
+      <c r="B40" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-    </row>
-    <row r="39" spans="2:15" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="75" t="s">
+      <c r="C40" s="79" t="s">
         <v>272</v>
       </c>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="75"/>
-      <c r="M39" s="75"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="75"/>
-    </row>
-    <row r="40" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="67" t="s">
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="79"/>
+      <c r="M40" s="79"/>
+      <c r="N40" s="79"/>
+      <c r="O40" s="79"/>
+    </row>
+    <row r="41" spans="2:15" ht="64.5" customHeight="1">
+      <c r="B41" s="68" t="s">
         <v>273</v>
       </c>
-      <c r="C40" s="75" t="s">
+      <c r="C41" s="79" t="s">
         <v>274</v>
       </c>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="75"/>
-      <c r="M40" s="75"/>
-      <c r="N40" s="75"/>
-      <c r="O40" s="75"/>
-    </row>
-    <row r="41" spans="2:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="68" t="s">
+      <c r="D41" s="79"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="79"/>
+      <c r="G41" s="79"/>
+      <c r="H41" s="79"/>
+      <c r="I41" s="79"/>
+      <c r="J41" s="79"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="79"/>
+      <c r="M41" s="79"/>
+      <c r="N41" s="79"/>
+      <c r="O41" s="79"/>
+    </row>
+    <row r="42" spans="2:15" ht="45" customHeight="1">
+      <c r="B42" s="69"/>
+    </row>
+    <row r="43" spans="2:15" ht="18" customHeight="1">
+      <c r="B43" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="C41" s="75" t="s">
+      <c r="C43" s="80"/>
+      <c r="D43" s="80"/>
+      <c r="E43" s="80"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="80"/>
+      <c r="L43" s="80"/>
+      <c r="M43" s="80"/>
+      <c r="N43" s="80"/>
+      <c r="O43" s="80"/>
+    </row>
+    <row r="44" spans="2:15" ht="69.75" customHeight="1">
+      <c r="B44" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="75"/>
-      <c r="M41" s="75"/>
-      <c r="N41" s="75"/>
-      <c r="O41" s="75"/>
-    </row>
-    <row r="42" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="69"/>
-    </row>
-    <row r="43" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="76" t="s">
+      <c r="C44" s="79"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="79"/>
+      <c r="F44" s="79"/>
+      <c r="G44" s="79"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="79"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="79"/>
+      <c r="L44" s="79"/>
+      <c r="M44" s="79"/>
+      <c r="N44" s="79"/>
+      <c r="O44" s="79"/>
+    </row>
+    <row r="45" spans="2:15" ht="31.5" customHeight="1">
+      <c r="B45" s="67" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="79" t="s">
         <v>277</v>
       </c>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
-      <c r="I43" s="76"/>
-      <c r="J43" s="76"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="76"/>
-      <c r="N43" s="76"/>
-      <c r="O43" s="76"/>
-    </row>
-    <row r="44" spans="2:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="75" t="s">
+      <c r="D45" s="79"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="79"/>
+      <c r="G45" s="79"/>
+      <c r="H45" s="79"/>
+      <c r="I45" s="79"/>
+      <c r="J45" s="79"/>
+      <c r="K45" s="79"/>
+      <c r="L45" s="79"/>
+      <c r="M45" s="79"/>
+      <c r="N45" s="79"/>
+      <c r="O45" s="79"/>
+    </row>
+    <row r="46" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B46" s="67" t="s">
+        <v>273</v>
+      </c>
+      <c r="C46" s="79" t="s">
         <v>278</v>
       </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="75"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="75"/>
-      <c r="K44" s="75"/>
-      <c r="L44" s="75"/>
-      <c r="M44" s="75"/>
-      <c r="N44" s="75"/>
-      <c r="O44" s="75"/>
-    </row>
-    <row r="45" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="67" t="s">
-        <v>273</v>
-      </c>
-      <c r="C45" s="75" t="s">
-        <v>279</v>
-      </c>
-      <c r="D45" s="75"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="75"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="75"/>
-      <c r="M45" s="75"/>
-      <c r="N45" s="75"/>
-      <c r="O45" s="75"/>
-    </row>
-    <row r="46" spans="2:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="67" t="s">
-        <v>275</v>
-      </c>
-      <c r="C46" s="75" t="s">
-        <v>280</v>
-      </c>
-      <c r="D46" s="75"/>
-      <c r="E46" s="75"/>
-      <c r="F46" s="75"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="75"/>
-      <c r="M46" s="75"/>
-      <c r="N46" s="75"/>
-      <c r="O46" s="75"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="79"/>
+      <c r="I46" s="79"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="79"/>
+      <c r="M46" s="79"/>
+      <c r="N46" s="79"/>
+      <c r="O46" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="25">

--- a/week_3/SyntheticData.xlsx
+++ b/week_3/SyntheticData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="2" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="2" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="17" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </externalReferences>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1137,7 +1137,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1280,7 +1280,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1486,6 +1485,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1627,11 +1627,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="301426752"/>
-        <c:axId val="301419304"/>
+        <c:axId val="273256992"/>
+        <c:axId val="312360424"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="301426752"/>
+        <c:axId val="273256992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1663,6 +1663,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1697,7 +1698,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301419304"/>
+        <c:crossAx val="312360424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1705,7 +1706,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="301419304"/>
+        <c:axId val="312360424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1746,6 +1747,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1780,7 +1782,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301426752"/>
+        <c:crossAx val="273256992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2194,11 +2196,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="301425184"/>
-        <c:axId val="301423224"/>
+        <c:axId val="273000688"/>
+        <c:axId val="312372296"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="301425184"/>
+        <c:axId val="273000688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2264,7 +2266,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301423224"/>
+        <c:crossAx val="312372296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2272,7 +2274,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="301423224"/>
+        <c:axId val="312372296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2347,7 +2349,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301425184"/>
+        <c:crossAx val="273000688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3550,7 +3552,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3753,7 +3755,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:O64" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:O62" totalsRowShown="0">
   <tableColumns count="15">
     <tableColumn id="1" name="loan_id" dataDxfId="12"/>
     <tableColumn id="2" name="inst_no" dataDxfId="11"/>
@@ -7046,7 +7048,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -7165,7 +7167,7 @@
         <v>Current</v>
       </c>
       <c r="O2" s="7">
-        <v>45969</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -7216,11 +7218,11 @@
         <v>0</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N64" si="1">IF(M3="","Current",IF(M3&lt;=0,"Current",IF(M3&lt;=7,"1–7",IF(M3&lt;=30,"8–30",IF(M3&lt;=60,"31–60",IF(M3&lt;=90,"61–90","90+"))))))</f>
+        <f t="shared" ref="N3:N62" si="1">IF(M3="","Current",IF(M3&lt;=0,"Current",IF(M3&lt;=7,"1–7",IF(M3&lt;=30,"8–30",IF(M3&lt;=60,"31–60",IF(M3&lt;=90,"61–90","90+"))))))</f>
         <v>Current</v>
       </c>
       <c r="O3" s="7">
-        <v>45970</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -7275,7 +7277,7 @@
         <v>Current</v>
       </c>
       <c r="O4" s="7">
-        <v>45971</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -7330,7 +7332,7 @@
         <v>Current</v>
       </c>
       <c r="O5" s="7">
-        <v>45972</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -7385,7 +7387,7 @@
         <v>Current</v>
       </c>
       <c r="O6" s="7">
-        <v>45973</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -7440,7 +7442,7 @@
         <v>Current</v>
       </c>
       <c r="O7" s="7">
-        <v>45974</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -7491,7 +7493,7 @@
         <v>Current</v>
       </c>
       <c r="O8" s="7">
-        <v>45975</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -7542,7 +7544,7 @@
         <v>Current</v>
       </c>
       <c r="O9" s="7">
-        <v>45976</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -7593,7 +7595,7 @@
         <v>Current</v>
       </c>
       <c r="O10" s="7">
-        <v>45977</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -7644,7 +7646,7 @@
         <v>Current</v>
       </c>
       <c r="O11" s="7">
-        <v>46008</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -7687,7 +7689,7 @@
         <v>84133.333333333328</v>
       </c>
       <c r="M12" s="37">
-        <f>MAX(0,L65-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L63-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N12" t="str">
@@ -7695,7 +7697,7 @@
         <v>Current</v>
       </c>
       <c r="O12" s="7">
-        <v>45979</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -7738,7 +7740,7 @@
         <v>126200</v>
       </c>
       <c r="M13" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>52</v>
       </c>
       <c r="N13" t="str">
@@ -7746,7 +7748,7 @@
         <v>31–60</v>
       </c>
       <c r="O13" s="7">
-        <v>45980</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -7790,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="37">
-        <f>MAX(0,L67-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L65-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N14" t="str">
@@ -7798,7 +7800,7 @@
         <v>Current</v>
       </c>
       <c r="O14" s="7">
-        <v>45981</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -7842,7 +7844,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="37">
-        <f>MAX(0,L68-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N15" t="str">
@@ -7850,7 +7852,7 @@
         <v>Current</v>
       </c>
       <c r="O15" s="7">
-        <v>45982</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -7894,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="37">
-        <f>MAX(0,L69-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L67-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N16" t="str">
@@ -7902,7 +7904,7 @@
         <v>Current</v>
       </c>
       <c r="O16" s="7">
-        <v>45983</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -7945,7 +7947,7 @@
         <v>57666.666666666664</v>
       </c>
       <c r="M17" s="37">
-        <f>MAX(0,L70-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L68-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N17" t="str">
@@ -7953,7 +7955,7 @@
         <v>Current</v>
       </c>
       <c r="O17" s="7">
-        <v>45984</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -7997,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="37">
-        <f>MAX(0,L71-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L69-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N18" t="str">
@@ -8005,7 +8007,7 @@
         <v>Current</v>
       </c>
       <c r="O18" s="7">
-        <v>45985</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -8053,7 +8055,7 @@
         <v>Current</v>
       </c>
       <c r="O19" s="7">
-        <v>45986</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -8108,7 +8110,7 @@
         <v>Current</v>
       </c>
       <c r="O20" s="7">
-        <v>45987</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -8163,7 +8165,7 @@
         <v>Current</v>
       </c>
       <c r="O21" s="7">
-        <v>45988</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -8210,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="37">
-        <f>MAX(0,L65-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L63-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N22" t="str">
@@ -8218,7 +8220,7 @@
         <v>Current</v>
       </c>
       <c r="O22" s="7">
-        <v>45989</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -8262,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>170</v>
       </c>
       <c r="N23" t="str">
@@ -8314,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>139</v>
       </c>
       <c r="N24" t="str">
@@ -8322,7 +8324,7 @@
         <v>90+</v>
       </c>
       <c r="O24" s="7">
-        <v>45991</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -8366,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>109</v>
       </c>
       <c r="N25" t="str">
@@ -8374,7 +8376,7 @@
         <v>90+</v>
       </c>
       <c r="O25" s="7">
-        <v>45992</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -8417,7 +8419,7 @@
         <v>18533.333333333332</v>
       </c>
       <c r="M26" s="37">
-        <f>MAX(0,L69-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L67-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N26" t="str">
@@ -8425,7 +8427,7 @@
         <v>Current</v>
       </c>
       <c r="O26" s="7">
-        <v>45993</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -8466,7 +8468,7 @@
       </c>
       <c r="K27" s="10"/>
       <c r="M27" s="37">
-        <f>MAX(0,L70-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L68-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N27" t="str">
@@ -8474,7 +8476,7 @@
         <v>Current</v>
       </c>
       <c r="O27" s="7">
-        <v>45994</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -8515,7 +8517,7 @@
       </c>
       <c r="K28" s="10"/>
       <c r="M28" s="37">
-        <f>MAX(0,L71-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L69-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N28" t="str">
@@ -8523,7 +8525,7 @@
         <v>Current</v>
       </c>
       <c r="O28" s="7">
-        <v>45995</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -8566,7 +8568,7 @@
         <v>38333.333333333336</v>
       </c>
       <c r="M29" s="37">
-        <f>MAX(0,L72-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L70-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N29" t="str">
@@ -8574,7 +8576,7 @@
         <v>Current</v>
       </c>
       <c r="O29" s="7">
-        <v>45996</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -8617,7 +8619,7 @@
         <v>76666.666666666672</v>
       </c>
       <c r="M30" s="37">
-        <f>MAX(0,L73-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L71-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N30" t="str">
@@ -8625,7 +8627,7 @@
         <v>Current</v>
       </c>
       <c r="O30" s="7">
-        <v>45997</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -8668,7 +8670,7 @@
         <v>115000</v>
       </c>
       <c r="M31" s="37">
-        <f>MAX(0,L74-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L72-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N31" t="str">
@@ -8676,7 +8678,7 @@
         <v>Current</v>
       </c>
       <c r="O31" s="7">
-        <v>45998</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -8720,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="37">
-        <f>MAX(0,L75-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L73-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N32" t="str">
@@ -8728,7 +8730,7 @@
         <v>Current</v>
       </c>
       <c r="O32" s="7">
-        <v>45999</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -8772,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="37">
-        <f>MAX(0,L76-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L74-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N33" t="str">
@@ -8780,7 +8782,7 @@
         <v>Current</v>
       </c>
       <c r="O33" s="7">
-        <v>46000</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="34" spans="1:15">
@@ -8824,7 +8826,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="37">
-        <f>MAX(0,L77-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L75-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N34" t="str">
@@ -8832,7 +8834,7 @@
         <v>Current</v>
       </c>
       <c r="O34" s="7">
-        <v>46001</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -8875,7 +8877,7 @@
         <v>53266.666666666664</v>
       </c>
       <c r="M35" s="37">
-        <f>MAX(0,L78-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L76-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N35" t="str">
@@ -8883,7 +8885,7 @@
         <v>Current</v>
       </c>
       <c r="O35" s="7">
-        <v>46002</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="36" spans="1:15">
@@ -8927,7 +8929,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="37">
-        <f>MAX(0,L79-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L77-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N36" t="str">
@@ -8935,7 +8937,7 @@
         <v>Current</v>
       </c>
       <c r="O36" s="7">
-        <v>46003</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -8979,7 +8981,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="37">
-        <f>MAX(0,L80-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L78-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N37" t="str">
@@ -8987,7 +8989,7 @@
         <v>Current</v>
       </c>
       <c r="O37" s="7">
-        <v>46004</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -9034,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="37">
-        <f>MAX(0,L81-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L79-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N38" t="str">
@@ -9042,7 +9044,7 @@
         <v>Current</v>
       </c>
       <c r="O38" s="7">
-        <v>46005</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -9089,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="37">
-        <f>MAX(0,L82-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L80-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N39" t="str">
@@ -9097,7 +9099,7 @@
         <v>Current</v>
       </c>
       <c r="O39" s="7">
-        <v>46006</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="40" spans="1:15">
@@ -9144,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="37">
-        <f>MAX(0,L83-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L81-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N40" t="str">
@@ -9152,7 +9154,7 @@
         <v>Current</v>
       </c>
       <c r="O40" s="7">
-        <v>46007</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -9196,7 +9198,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>164</v>
       </c>
       <c r="N41" t="str">
@@ -9204,7 +9206,7 @@
         <v>90+</v>
       </c>
       <c r="O41" s="7">
-        <v>46008</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="42" spans="1:15">
@@ -9248,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>133</v>
       </c>
       <c r="N42" t="str">
@@ -9256,7 +9258,7 @@
         <v>90+</v>
       </c>
       <c r="O42" s="7">
-        <v>46009</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="43" spans="1:15">
@@ -9300,7 +9302,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>103</v>
       </c>
       <c r="N43" t="str">
@@ -9308,7 +9310,7 @@
         <v>90+</v>
       </c>
       <c r="O43" s="7">
-        <v>46010</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="44" spans="1:15">
@@ -9339,7 +9341,7 @@
       <c r="J44" s="12"/>
       <c r="K44" s="10"/>
       <c r="M44" s="37">
-        <f>MAX(0,L87-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L85-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N44" t="str">
@@ -9347,7 +9349,7 @@
         <v>Current</v>
       </c>
       <c r="O44" s="7">
-        <v>46011</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="45" spans="1:15">
@@ -9378,7 +9380,7 @@
       <c r="J45" s="12"/>
       <c r="K45" s="10"/>
       <c r="M45" s="37">
-        <f>MAX(0,L88-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L86-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N45" t="str">
@@ -9386,7 +9388,7 @@
         <v>Current</v>
       </c>
       <c r="O45" s="7">
-        <v>46012</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="46" spans="1:15">
@@ -9417,7 +9419,7 @@
       <c r="J46" s="12"/>
       <c r="K46" s="10"/>
       <c r="M46" s="37">
-        <f>MAX(0,L89-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L87-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N46" t="str">
@@ -9425,7 +9427,7 @@
         <v>Current</v>
       </c>
       <c r="O46" s="7">
-        <v>46013</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="47" spans="1:15">
@@ -9456,7 +9458,7 @@
       <c r="J47" s="12"/>
       <c r="K47" s="12"/>
       <c r="M47" s="37">
-        <f>MAX(0,L90-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L88-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N47" t="str">
@@ -9464,7 +9466,7 @@
         <v>Current</v>
       </c>
       <c r="O47" s="7">
-        <v>46014</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="48" spans="1:15">
@@ -9495,7 +9497,7 @@
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
       <c r="M48" s="37">
-        <f>MAX(0,L91-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L89-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N48" t="str">
@@ -9503,7 +9505,7 @@
         <v>Current</v>
       </c>
       <c r="O48" s="7">
-        <v>46015</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -9534,7 +9536,7 @@
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
       <c r="M49" s="37">
-        <f>MAX(0,L92-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L90-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N49" t="str">
@@ -9542,7 +9544,7 @@
         <v>Current</v>
       </c>
       <c r="O49" s="7">
-        <v>46016</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="50" spans="1:15">
@@ -9586,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="37">
-        <f>MAX(0,L93-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L91-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N50" t="str">
@@ -9594,7 +9596,7 @@
         <v>Current</v>
       </c>
       <c r="O50" s="7">
-        <v>46017</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="51" spans="1:15">
@@ -9638,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="37">
-        <f>MAX(0,L94-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L92-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N51" t="str">
@@ -9646,7 +9648,7 @@
         <v>Current</v>
       </c>
       <c r="O51" s="7">
-        <v>46018</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="52" spans="1:15">
@@ -9690,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="37">
-        <f>MAX(0,L95-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L93-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N52" t="str">
@@ -9698,7 +9700,7 @@
         <v>Current</v>
       </c>
       <c r="O52" s="7">
-        <v>46019</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="53" spans="1:15">
@@ -9729,7 +9731,7 @@
       <c r="J53" s="12"/>
       <c r="K53" s="10"/>
       <c r="M53" s="37">
-        <f>MAX(0,L96-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L94-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N53" t="str">
@@ -9737,7 +9739,7 @@
         <v>Current</v>
       </c>
       <c r="O53" s="7">
-        <v>46020</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="54" spans="1:15">
@@ -9768,7 +9770,7 @@
       <c r="J54" s="12"/>
       <c r="K54" s="10"/>
       <c r="M54" s="37">
-        <f>MAX(0,L97-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L95-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N54" t="str">
@@ -9776,7 +9778,7 @@
         <v>Current</v>
       </c>
       <c r="O54" s="7">
-        <v>46021</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="55" spans="1:15">
@@ -9807,7 +9809,7 @@
       <c r="J55" s="12"/>
       <c r="K55" s="10"/>
       <c r="M55" s="37">
-        <f>MAX(0,L98-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L96-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N55" t="str">
@@ -9815,7 +9817,7 @@
         <v>Current</v>
       </c>
       <c r="O55" s="7">
-        <v>46022</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="56" spans="1:15">
@@ -9862,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="37">
-        <f>MAX(0,L99-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L97-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N56" t="str">
@@ -9870,7 +9872,7 @@
         <v>Current</v>
       </c>
       <c r="O56" s="7">
-        <v>46023</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="57" spans="1:15">
@@ -9917,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="37">
-        <f>MAX(0,L100-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L98-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N57" t="str">
@@ -9925,7 +9927,7 @@
         <v>Current</v>
       </c>
       <c r="O57" s="7">
-        <v>46024</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="58" spans="1:15">
@@ -9972,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="37">
-        <f>MAX(0,L101-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L99-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N58" t="str">
@@ -9980,7 +9982,7 @@
         <v>Current</v>
       </c>
       <c r="O58" s="7">
-        <v>46025</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="59" spans="1:15">
@@ -10020,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>158</v>
       </c>
       <c r="N59" t="str">
@@ -10028,7 +10030,7 @@
         <v>90+</v>
       </c>
       <c r="O59" s="7">
-        <v>46026</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="60" spans="1:15">
@@ -10068,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>127</v>
       </c>
       <c r="N60" t="str">
@@ -10076,7 +10078,7 @@
         <v>90+</v>
       </c>
       <c r="O60" s="7">
-        <v>46027</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -10116,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="37">
-        <f>MAX(0,L66-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L64-Table1[[#This Row],[due_date]])</f>
         <v>97</v>
       </c>
       <c r="N61" t="str">
@@ -10124,7 +10126,7 @@
         <v>90+</v>
       </c>
       <c r="O61" s="7">
-        <v>46028</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="62" spans="1:15">
@@ -10137,7 +10139,7 @@
       <c r="J62" s="12"/>
       <c r="K62" s="10"/>
       <c r="M62" s="37">
-        <f>MAX(0,L105-Table1[[#This Row],[due_date]])</f>
+        <f>MAX(0,L103-Table1[[#This Row],[due_date]])</f>
         <v>0</v>
       </c>
       <c r="N62" t="str">
@@ -10145,56 +10147,14 @@
         <v>Current</v>
       </c>
       <c r="O62" s="7">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="G63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="10"/>
-      <c r="M63" s="37">
-        <f>MAX(0,L104-Table1[[#This Row],[due_date]])</f>
-        <v>0</v>
-      </c>
-      <c r="N63" t="str">
-        <f t="shared" si="1"/>
-        <v>Current</v>
-      </c>
-      <c r="O63" s="78">
-        <f>L123</f>
-        <v>0</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="64" spans="1:15">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="G64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="10"/>
-      <c r="M64" s="37">
-        <f>MAX(0,L105-Table1[[#This Row],[due_date]])</f>
-        <v>0</v>
-      </c>
-      <c r="N64" t="str">
-        <f t="shared" si="1"/>
-        <v>Current</v>
-      </c>
-      <c r="O64" s="78">
-        <f>L124</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="11:12">
-      <c r="K66" s="2" t="s">
+      <c r="K64" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="L66" s="7">
+      <c r="L64" s="7">
         <v>46050</v>
       </c>
     </row>
@@ -10662,67 +10622,67 @@
       <c r="B6" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="85">
+      <c r="C6" s="84">
         <v>46050</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="F6" s="86" t="s">
+      <c r="D6" s="84"/>
+      <c r="F6" s="85" t="s">
         <v>246</v>
       </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
     </row>
     <row r="7" spans="2:21" ht="15" customHeight="1">
       <c r="B7" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="D7" s="87"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
     </row>
     <row r="8" spans="2:21" ht="15" customHeight="1">
       <c r="B8" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="D8" s="87"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="2:21" ht="15" customHeight="1">
       <c r="B9" s="52" t="s">
         <v>223</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="87"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
     </row>
     <row r="11" spans="2:21" ht="15" customHeight="1">
       <c r="B11" s="51" t="s">
@@ -10736,113 +10696,113 @@
       </c>
     </row>
     <row r="13" spans="2:21" ht="15" customHeight="1">
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81" t="s">
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81" t="s">
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81" t="s">
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81" t="s">
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81" t="s">
+      <c r="O13" s="80"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="80" t="s">
         <v>206</v>
       </c>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
     </row>
     <row r="14" spans="2:21" ht="15" customHeight="1">
-      <c r="B14" s="82">
+      <c r="B14" s="81">
         <v>20</v>
       </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82">
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*('[1]Calc - Loan Summary'!$O$5:$O$24&gt;0)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="83">
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="82">
         <f>SUM(Installment!H8:H61)</f>
         <v>431666.66666666657</v>
       </c>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83">
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82">
         <f>SUM(Installment!D2:D61)</f>
         <v>2520299.9999999995</v>
       </c>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83">
+      <c r="L14" s="82"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="82">
         <f>SUM(Installment!J2:J61)</f>
         <v>3416466.666666667</v>
       </c>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="84">
+      <c r="O14" s="82"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="83">
         <f>IFERROR(N14/K14,0)</f>
         <v>1.3555793622452357</v>
       </c>
-      <c r="R14" s="84"/>
-      <c r="S14" s="84"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
     </row>
     <row r="15" spans="2:21" ht="15" customHeight="1">
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="82"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="83"/>
     </row>
     <row r="16" spans="2:21" ht="15" customHeight="1">
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="83"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84"/>
-      <c r="S16" s="84"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="82"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="83"/>
+      <c r="S16" s="83"/>
     </row>
     <row r="18" spans="2:7" ht="15" customHeight="1">
       <c r="B18" s="51" t="s">
@@ -11182,159 +11142,159 @@
       </c>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1">
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="79" t="s">
         <v>269</v>
       </c>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="80"/>
-      <c r="M38" s="80"/>
-      <c r="N38" s="80"/>
-      <c r="O38" s="80"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="79"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="79"/>
+      <c r="M38" s="79"/>
+      <c r="N38" s="79"/>
+      <c r="O38" s="79"/>
     </row>
     <row r="39" spans="2:15" ht="84.75" customHeight="1">
-      <c r="B39" s="79" t="s">
+      <c r="B39" s="78" t="s">
         <v>270</v>
       </c>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="79"/>
-      <c r="N39" s="79"/>
-      <c r="O39" s="79"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="78"/>
+      <c r="K39" s="78"/>
+      <c r="L39" s="78"/>
+      <c r="M39" s="78"/>
+      <c r="N39" s="78"/>
+      <c r="O39" s="78"/>
     </row>
     <row r="40" spans="2:15" ht="18" customHeight="1">
       <c r="B40" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="78" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="79"/>
-      <c r="M40" s="79"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="79"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="78"/>
+      <c r="L40" s="78"/>
+      <c r="M40" s="78"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="78"/>
     </row>
     <row r="41" spans="2:15" ht="64.5" customHeight="1">
       <c r="B41" s="68" t="s">
         <v>273</v>
       </c>
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="78" t="s">
         <v>274</v>
       </c>
-      <c r="D41" s="79"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="79"/>
-      <c r="G41" s="79"/>
-      <c r="H41" s="79"/>
-      <c r="I41" s="79"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="79"/>
-      <c r="L41" s="79"/>
-      <c r="M41" s="79"/>
-      <c r="N41" s="79"/>
-      <c r="O41" s="79"/>
+      <c r="D41" s="78"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="78"/>
+      <c r="I41" s="78"/>
+      <c r="J41" s="78"/>
+      <c r="K41" s="78"/>
+      <c r="L41" s="78"/>
+      <c r="M41" s="78"/>
+      <c r="N41" s="78"/>
+      <c r="O41" s="78"/>
     </row>
     <row r="42" spans="2:15" ht="45" customHeight="1">
       <c r="B42" s="69"/>
     </row>
     <row r="43" spans="2:15" ht="18" customHeight="1">
-      <c r="B43" s="80" t="s">
+      <c r="B43" s="79" t="s">
         <v>275</v>
       </c>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="80"/>
-      <c r="L43" s="80"/>
-      <c r="M43" s="80"/>
-      <c r="N43" s="80"/>
-      <c r="O43" s="80"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="79"/>
     </row>
     <row r="44" spans="2:15" ht="69.75" customHeight="1">
-      <c r="B44" s="79" t="s">
+      <c r="B44" s="78" t="s">
         <v>276</v>
       </c>
-      <c r="C44" s="79"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
-      <c r="F44" s="79"/>
-      <c r="G44" s="79"/>
-      <c r="H44" s="79"/>
-      <c r="I44" s="79"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="79"/>
-      <c r="L44" s="79"/>
-      <c r="M44" s="79"/>
-      <c r="N44" s="79"/>
-      <c r="O44" s="79"/>
+      <c r="C44" s="78"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="78"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="78"/>
     </row>
     <row r="45" spans="2:15" ht="31.5" customHeight="1">
       <c r="B45" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="78" t="s">
         <v>277</v>
       </c>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
-      <c r="F45" s="79"/>
-      <c r="G45" s="79"/>
-      <c r="H45" s="79"/>
-      <c r="I45" s="79"/>
-      <c r="J45" s="79"/>
-      <c r="K45" s="79"/>
-      <c r="L45" s="79"/>
-      <c r="M45" s="79"/>
-      <c r="N45" s="79"/>
-      <c r="O45" s="79"/>
+      <c r="D45" s="78"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="78"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="78"/>
+      <c r="L45" s="78"/>
+      <c r="M45" s="78"/>
+      <c r="N45" s="78"/>
+      <c r="O45" s="78"/>
     </row>
     <row r="46" spans="2:15" ht="54.75" customHeight="1">
       <c r="B46" s="67" t="s">
         <v>273</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="78" t="s">
         <v>278</v>
       </c>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="79"/>
-      <c r="G46" s="79"/>
-      <c r="H46" s="79"/>
-      <c r="I46" s="79"/>
-      <c r="J46" s="79"/>
-      <c r="K46" s="79"/>
-      <c r="L46" s="79"/>
-      <c r="M46" s="79"/>
-      <c r="N46" s="79"/>
-      <c r="O46" s="79"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="78"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="78"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="78"/>
+      <c r="N46" s="78"/>
+      <c r="O46" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="25">
